--- a/estadistica2/data/perez_rojas.xlsx
+++ b/estadistica2/data/perez_rojas.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10329"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{418A3BC1-EDFB-3A43-A0B0-94170C65A0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EDE3144-B69E-3346-A4C5-D40C14E80566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{52DB9F00-0124-4305-9E14-A1996DB4BA91}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" activeTab="2" xr2:uid="{52DB9F00-0124-4305-9E14-A1996DB4BA91}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet name="codebook" sheetId="2" r:id="rId2"/>
+    <sheet name="variables" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2986" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2994" uniqueCount="99">
   <si>
     <t>Albania</t>
   </si>
@@ -314,6 +315,30 @@
   <si>
     <t>descripción</t>
   </si>
+  <si>
+    <t>VD</t>
+  </si>
+  <si>
+    <t>VI1</t>
+  </si>
+  <si>
+    <t>VI2</t>
+  </si>
+  <si>
+    <t>VI3</t>
+  </si>
+  <si>
+    <t>VI4</t>
+  </si>
+  <si>
+    <t>medicion</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
 </sst>
 </file>
 
@@ -397,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -405,8 +430,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -749,29 +773,29 @@
     <col min="4" max="8" width="8.6640625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="1" t="s">
         <v>88</v>
       </c>
     </row>
@@ -36357,55 +36381,99 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F175B-6C70-2142-92AF-032577D29729}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
+      <c r="C1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
         <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C24629F7-CB4C-E143-8895-FF20F3021085}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
